--- a/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R282-CNAMAmeliSecteurConventionnement.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/CodeSystem-TRE-R282-CNAMAmeliSecteurConventionnement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -220,13 +220,19 @@
     <t>0</t>
   </si>
   <si>
+    <t>Conventionné</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Conventionné Dépassement Permanent</t>
+    <t>Conventionné avec dépassement</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>Conventionné avec honoraires libres</t>
   </si>
 </sst>
 </file>
@@ -721,7 +727,7 @@
         <v>58</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -730,10 +736,10 @@
         <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -742,10 +748,10 @@
         <v>58</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2"/>
     </row>
